--- a/Budget1.xlsx
+++ b/Budget1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\NewGit\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402BC44D-A772-4A87-B98F-8B0E3D36B792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F77F377-436D-4DA8-9702-E800F68C8504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="29" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="27" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
   <sheets>
     <sheet name="Fevrier" sheetId="3" r:id="rId1"/>
@@ -40,14 +40,15 @@
     <sheet name="DEC24" sheetId="44" r:id="rId25"/>
     <sheet name="JANV25" sheetId="45" r:id="rId26"/>
     <sheet name="FEVR25" sheetId="46" r:id="rId27"/>
-    <sheet name="Credit" sheetId="28" r:id="rId28"/>
-    <sheet name="Entreprise" sheetId="35" r:id="rId29"/>
-    <sheet name="Construction " sheetId="27" r:id="rId30"/>
-    <sheet name="Construction2" sheetId="39" r:id="rId31"/>
-    <sheet name="Terrain" sheetId="18" r:id="rId32"/>
-    <sheet name="Poulailler" sheetId="20" r:id="rId33"/>
-    <sheet name="divers " sheetId="22" r:id="rId34"/>
-    <sheet name="MB MEACSYTEM" sheetId="40" r:id="rId35"/>
+    <sheet name="Mars25" sheetId="47" r:id="rId28"/>
+    <sheet name="Credit" sheetId="28" r:id="rId29"/>
+    <sheet name="Entreprise" sheetId="35" r:id="rId30"/>
+    <sheet name="Construction " sheetId="27" r:id="rId31"/>
+    <sheet name="Construction2" sheetId="39" r:id="rId32"/>
+    <sheet name="Terrain" sheetId="18" r:id="rId33"/>
+    <sheet name="Poulailler" sheetId="20" r:id="rId34"/>
+    <sheet name="divers " sheetId="22" r:id="rId35"/>
+    <sheet name="MB MEACSYTEM" sheetId="40" r:id="rId36"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1727" uniqueCount="455">
   <si>
     <t>Loyer</t>
   </si>
@@ -1376,6 +1377,63 @@
   </si>
   <si>
     <t>Main d'œuvre carreau</t>
+  </si>
+  <si>
+    <t>forage</t>
+  </si>
+  <si>
+    <t>Chambre 1</t>
+  </si>
+  <si>
+    <t>Chambre 2</t>
+  </si>
+  <si>
+    <t>Salon</t>
+  </si>
+  <si>
+    <t>Couloir</t>
+  </si>
+  <si>
+    <t>Garage</t>
+  </si>
+  <si>
+    <t>devant salon</t>
+  </si>
+  <si>
+    <t>patio 1</t>
+  </si>
+  <si>
+    <t>patio 2</t>
+  </si>
+  <si>
+    <t>Carreau Sol</t>
+  </si>
+  <si>
+    <t>Carreau Toilet Sol</t>
+  </si>
+  <si>
+    <t>Toilette 1</t>
+  </si>
+  <si>
+    <t>Tolette 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrau Facade </t>
+  </si>
+  <si>
+    <t>toilette 1</t>
+  </si>
+  <si>
+    <t>toilette 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuisisne </t>
+  </si>
+  <si>
+    <t>Carreau cuisine sol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total </t>
   </si>
 </sst>
 </file>
@@ -22482,6 +22540,1261 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{203118BA-A9DA-4209-85B1-21AB2F24CB40}">
+  <dimension ref="A1:T125"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.125" customWidth="1"/>
+    <col min="9" max="9" width="19.625" customWidth="1"/>
+    <col min="11" max="11" width="8.125" customWidth="1"/>
+    <col min="13" max="13" width="18.125" customWidth="1"/>
+    <col min="18" max="18" width="3.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="10"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="10"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="J3" s="12"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="12"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="10"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11">
+        <f>2200+3000+1000</f>
+        <v>6200</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="O4" s="11">
+        <v>1480</v>
+      </c>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="12"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="10"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="12"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="10"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="15"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I6" s="14"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="L6" s="15"/>
+      <c r="M6" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="N6" s="15"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="12"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="10"/>
+      <c r="B7" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="F7" s="11">
+        <v>1012</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="N7" s="11">
+        <v>150</v>
+      </c>
+      <c r="O7" s="11"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="12"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="F8" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="N8" s="11">
+        <v>200</v>
+      </c>
+      <c r="O8" s="11"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="12"/>
+      <c r="T8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="11">
+        <v>400</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="F9" s="11">
+        <v>96</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="N9" s="11">
+        <v>200</v>
+      </c>
+      <c r="O9" s="11"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="12"/>
+      <c r="T9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+      <c r="B10" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="F10" s="11">
+        <v>50</v>
+      </c>
+      <c r="G10" s="11"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="N10" s="11">
+        <v>300</v>
+      </c>
+      <c r="O10" s="11"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="12"/>
+      <c r="T10">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="10"/>
+      <c r="B11" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="C11" s="11">
+        <v>39</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="11">
+        <v>157</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="N11" s="11">
+        <v>100</v>
+      </c>
+      <c r="O11" s="11"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="12"/>
+      <c r="T11">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="C12" s="11">
+        <v>1500</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="11">
+        <v>300</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="N12" s="11">
+        <v>13</v>
+      </c>
+      <c r="O12" s="11"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="12"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="10"/>
+      <c r="B13" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="F13" s="11">
+        <v>52</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="N13" s="11">
+        <v>13</v>
+      </c>
+      <c r="O13" s="11"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="12"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="10"/>
+      <c r="B14" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="11">
+        <v>13</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="12"/>
+      <c r="T14">
+        <f>SUM(T8:T11)</f>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+      <c r="B15" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="F15" s="11">
+        <v>100</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="12"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="C16" s="11">
+        <v>247</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="F16" s="11">
+        <v>131</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="12"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="10"/>
+      <c r="B17" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="12"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="10"/>
+      <c r="B18" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="12"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="10"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="12"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="12"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="12"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="10"/>
+      <c r="B22" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="11">
+        <f>SUM(C7:C19)</f>
+        <v>2186</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11">
+        <f>SUM(F7:F20)+150</f>
+        <v>3061</v>
+      </c>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11">
+        <f>SUM(I7:I19)</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="12"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11">
+        <f>SUM(N7:N19)</f>
+        <v>976</v>
+      </c>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11">
+        <f>SUM(Q7:Q18)</f>
+        <v>0</v>
+      </c>
+      <c r="R22" s="11"/>
+      <c r="S22" s="12"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="12"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="12"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="12"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="11">
+        <f>C22+F22+I22</f>
+        <v>5247</v>
+      </c>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11">
+        <f>N22+Q22</f>
+        <v>976</v>
+      </c>
+      <c r="Q26" s="11"/>
+      <c r="R26" s="11"/>
+      <c r="S26" s="12"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" s="10"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11"/>
+      <c r="R27" s="11"/>
+      <c r="S27" s="12"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="11"/>
+      <c r="Q28" s="11"/>
+      <c r="R28" s="11"/>
+      <c r="S28" s="12"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" s="10"/>
+      <c r="B29" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="C29" s="11">
+        <f>ABS(G4-D26)</f>
+        <v>5247</v>
+      </c>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="L29" s="11">
+        <f>O4-P26</f>
+        <v>504</v>
+      </c>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="12"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="11"/>
+      <c r="S30" s="12"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="12"/>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="12"/>
+      <c r="R31" s="12"/>
+      <c r="S31" s="12"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="12"/>
+      <c r="P32" s="12"/>
+      <c r="Q32" s="12"/>
+      <c r="R32" s="12"/>
+      <c r="S32" s="12"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="11"/>
+      <c r="P33" s="11"/>
+      <c r="Q33" s="11"/>
+      <c r="R33" s="11"/>
+      <c r="S33" s="11"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34" s="9"/>
+      <c r="B34" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C34" s="11">
+        <f>H4-D26</f>
+        <v>953</v>
+      </c>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11">
+        <f>C29+L29</f>
+        <v>5751</v>
+      </c>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="11"/>
+      <c r="R34" s="11"/>
+      <c r="S34" s="11"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35" s="9"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="11"/>
+      <c r="P35" s="11"/>
+      <c r="Q35" s="11"/>
+      <c r="R35" s="11"/>
+      <c r="S35" s="11"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E36">
+        <f>5.2+13.8+10.96+13+13+21+6.99+47+62+12+68+40</f>
+        <v>312.95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I39" t="s">
+        <v>376</v>
+      </c>
+      <c r="J39">
+        <v>39</v>
+      </c>
+      <c r="L39" t="s">
+        <v>382</v>
+      </c>
+      <c r="M39">
+        <f>SUM(J39:J58)</f>
+        <v>22002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E40" s="22" t="s">
+        <v>364</v>
+      </c>
+      <c r="F40">
+        <v>500</v>
+      </c>
+      <c r="I40" t="s">
+        <v>377</v>
+      </c>
+      <c r="J40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E41" s="22" t="s">
+        <v>365</v>
+      </c>
+      <c r="F41">
+        <v>800</v>
+      </c>
+      <c r="I41" t="s">
+        <v>378</v>
+      </c>
+      <c r="J41">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E42" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="F42">
+        <v>200</v>
+      </c>
+      <c r="I42" t="s">
+        <v>379</v>
+      </c>
+      <c r="J42">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E43" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="F43">
+        <v>2000</v>
+      </c>
+      <c r="I43" t="s">
+        <v>380</v>
+      </c>
+      <c r="J43">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E44" s="22" t="s">
+        <v>373</v>
+      </c>
+      <c r="F44">
+        <v>500</v>
+      </c>
+      <c r="I44" t="s">
+        <v>380</v>
+      </c>
+      <c r="J44">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E45" s="22" t="s">
+        <v>368</v>
+      </c>
+      <c r="F45">
+        <v>100</v>
+      </c>
+      <c r="I45" t="s">
+        <v>381</v>
+      </c>
+      <c r="J45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E46" s="22" t="s">
+        <v>369</v>
+      </c>
+      <c r="F46">
+        <v>67</v>
+      </c>
+      <c r="I46" t="s">
+        <v>101</v>
+      </c>
+      <c r="J46">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E47" s="22" t="s">
+        <v>370</v>
+      </c>
+      <c r="F47">
+        <v>50</v>
+      </c>
+      <c r="I47" t="s">
+        <v>383</v>
+      </c>
+      <c r="J47">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E48" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="F48">
+        <v>70</v>
+      </c>
+      <c r="I48" t="s">
+        <v>384</v>
+      </c>
+      <c r="J48">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E49" s="22" t="s">
+        <v>372</v>
+      </c>
+      <c r="F49">
+        <v>300</v>
+      </c>
+      <c r="I49" t="s">
+        <v>385</v>
+      </c>
+      <c r="J49">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E50" s="22" t="s">
+        <v>374</v>
+      </c>
+      <c r="F50">
+        <v>100</v>
+      </c>
+      <c r="I50" t="s">
+        <v>108</v>
+      </c>
+      <c r="J50">
+        <v>20914</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I51" t="s">
+        <v>387</v>
+      </c>
+      <c r="J51">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J52">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F54">
+        <f>SUM(F40:F50)</f>
+        <v>4687</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B62" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62" s="11">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="98" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B98">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="99" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B99">
+        <v>2500</v>
+      </c>
+      <c r="J99">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="100" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B100">
+        <v>2500</v>
+      </c>
+      <c r="J100">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="101" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B101">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="102" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B102">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="106" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B106">
+        <f>SUM(B98:B102)</f>
+        <v>9500</v>
+      </c>
+      <c r="D106">
+        <f>B106-7000</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="107" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P107">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="108" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P108" s="11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P109" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P110" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P111" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="P112" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="113" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="P113" s="11">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="114" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="P114" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E115">
+        <v>1400</v>
+      </c>
+      <c r="P115" s="11">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="116" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E116">
+        <v>1300</v>
+      </c>
+      <c r="P116" s="11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="117" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E117">
+        <v>950</v>
+      </c>
+      <c r="P117" s="11"/>
+    </row>
+    <row r="118" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="P118" s="11">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="121" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E121">
+        <f>SUM(E115:E119)</f>
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="125" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="P125">
+        <f>SUM(P105:P122)</f>
+        <v>516.99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B974066F-70AB-4CE0-9413-18C0CA619219}">
   <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -22890,540 +24203,6 @@
       <c r="F41" s="18">
         <f>SUM(B41:E41)</f>
         <v>2000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A0FB8E-CB12-475E-9D50-00930E5BD370}">
-  <dimension ref="A1:J36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.75" customWidth="1"/>
-    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.25" customWidth="1"/>
-    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C1" t="s">
-        <v>281</v>
-      </c>
-      <c r="D1" t="s">
-        <v>282</v>
-      </c>
-      <c r="E1" t="s">
-        <v>279</v>
-      </c>
-      <c r="F1" t="s">
-        <v>280</v>
-      </c>
-      <c r="G1" t="s">
-        <v>283</v>
-      </c>
-      <c r="I1" t="s">
-        <v>314</v>
-      </c>
-      <c r="J1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>284</v>
-      </c>
-      <c r="B2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C2" s="20">
-        <v>9456</v>
-      </c>
-      <c r="D2" s="20">
-        <f>C2+(C2*20%)</f>
-        <v>11347.2</v>
-      </c>
-      <c r="E2" s="20">
-        <f>C2*21%</f>
-        <v>1985.76</v>
-      </c>
-      <c r="F2" s="20">
-        <f>C2-E2</f>
-        <v>7470.24</v>
-      </c>
-      <c r="G2" s="20">
-        <f>D2-C2</f>
-        <v>1891.2000000000007</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>285</v>
-      </c>
-      <c r="B3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C3" s="5">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5">
-        <f>C3+(C3*20%)</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="5">
-        <f>C3*21%</f>
-        <v>0</v>
-      </c>
-      <c r="F3" s="5">
-        <f>C3-E3</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="5">
-        <f>D3-C3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>311</v>
-      </c>
-      <c r="C5">
-        <f>C2+C3</f>
-        <v>9456</v>
-      </c>
-      <c r="D5">
-        <f>D2+D3</f>
-        <v>11347.2</v>
-      </c>
-      <c r="E5" s="5">
-        <f>E2+E3</f>
-        <v>1985.76</v>
-      </c>
-      <c r="F5" s="19">
-        <f>F2+F3</f>
-        <v>7470.24</v>
-      </c>
-      <c r="G5" s="5">
-        <f>G2+G3</f>
-        <v>1891.2000000000007</v>
-      </c>
-      <c r="I5">
-        <f>E5+G5</f>
-        <v>3876.9600000000009</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>284</v>
-      </c>
-      <c r="B9" t="s">
-        <v>310</v>
-      </c>
-      <c r="C9" s="20">
-        <v>9600</v>
-      </c>
-      <c r="D9" s="20">
-        <f>C9+(C9*20%)</f>
-        <v>11520</v>
-      </c>
-      <c r="E9" s="20">
-        <f>C9*21%</f>
-        <v>2016</v>
-      </c>
-      <c r="F9" s="20">
-        <f>C9-E9</f>
-        <v>7584</v>
-      </c>
-      <c r="G9" s="20">
-        <f>D9-C9</f>
-        <v>1920</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>285</v>
-      </c>
-      <c r="B10" t="s">
-        <v>310</v>
-      </c>
-      <c r="C10" s="5">
-        <f>1300+3200+600</f>
-        <v>5100</v>
-      </c>
-      <c r="D10" s="5">
-        <f>C10+(C10*20%)</f>
-        <v>6120</v>
-      </c>
-      <c r="E10" s="5">
-        <f>C10*21%</f>
-        <v>1071</v>
-      </c>
-      <c r="F10" s="5">
-        <f>C10-E10</f>
-        <v>4029</v>
-      </c>
-      <c r="G10" s="5">
-        <f>D10-C10</f>
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>312</v>
-      </c>
-      <c r="C12">
-        <f>C9+C10</f>
-        <v>14700</v>
-      </c>
-      <c r="D12">
-        <f>D9+D10</f>
-        <v>17640</v>
-      </c>
-      <c r="E12" s="5">
-        <f>E9+E10</f>
-        <v>3087</v>
-      </c>
-      <c r="F12" s="19">
-        <f>F9+F10</f>
-        <v>11613</v>
-      </c>
-      <c r="G12" s="5">
-        <f>G9+G10</f>
-        <v>2940</v>
-      </c>
-      <c r="I12">
-        <f>E12+G12</f>
-        <v>6027</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>284</v>
-      </c>
-      <c r="B15" t="s">
-        <v>361</v>
-      </c>
-      <c r="C15" s="20">
-        <v>12000</v>
-      </c>
-      <c r="D15" s="20">
-        <f>C15+(C15*20%)</f>
-        <v>14400</v>
-      </c>
-      <c r="E15" s="20">
-        <f>C15*21%</f>
-        <v>2520</v>
-      </c>
-      <c r="F15" s="20">
-        <f>C15-E15</f>
-        <v>9480</v>
-      </c>
-      <c r="G15" s="20">
-        <f>D15-C15</f>
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>285</v>
-      </c>
-      <c r="B16" t="s">
-        <v>361</v>
-      </c>
-      <c r="C16" s="5">
-        <f>3000+3750+3375</f>
-        <v>10125</v>
-      </c>
-      <c r="D16" s="5">
-        <f>C16+(C16*20%)</f>
-        <v>12150</v>
-      </c>
-      <c r="E16" s="5">
-        <f>C16*21%</f>
-        <v>2126.25</v>
-      </c>
-      <c r="F16" s="5">
-        <f>C16-E16</f>
-        <v>7998.75</v>
-      </c>
-      <c r="G16" s="5">
-        <f>D16-C16</f>
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18">
-        <f>C15+C16</f>
-        <v>22125</v>
-      </c>
-      <c r="D18">
-        <f>D15+D16</f>
-        <v>26550</v>
-      </c>
-      <c r="E18" s="5">
-        <f>E15+E16</f>
-        <v>4646.25</v>
-      </c>
-      <c r="F18" s="19">
-        <f>F15+F16</f>
-        <v>17478.75</v>
-      </c>
-      <c r="G18" s="5">
-        <f>G15+G16</f>
-        <v>4425</v>
-      </c>
-      <c r="I18">
-        <f>F18-4100</f>
-        <v>13378.75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>284</v>
-      </c>
-      <c r="B21" t="s">
-        <v>218</v>
-      </c>
-      <c r="C21" s="20">
-        <v>0</v>
-      </c>
-      <c r="D21" s="20">
-        <f>C21+(C21*20%)</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="20">
-        <f>C21*21%</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="20">
-        <f>C21-E21</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="20">
-        <f>D21-C21</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>285</v>
-      </c>
-      <c r="B22" t="s">
-        <v>361</v>
-      </c>
-      <c r="C22" s="5">
-        <v>19000</v>
-      </c>
-      <c r="D22" s="5">
-        <f>C22+(C22*20%)</f>
-        <v>22800</v>
-      </c>
-      <c r="E22" s="5">
-        <f>C22*23%</f>
-        <v>4370</v>
-      </c>
-      <c r="F22" s="5">
-        <f>C22-E22</f>
-        <v>14630</v>
-      </c>
-      <c r="G22" s="5">
-        <f>D22-C22</f>
-        <v>3800</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>362</v>
-      </c>
-      <c r="C24">
-        <f>C21+C22</f>
-        <v>19000</v>
-      </c>
-      <c r="D24">
-        <f>D21+D22</f>
-        <v>22800</v>
-      </c>
-      <c r="E24" s="5">
-        <f>E21+E22</f>
-        <v>4370</v>
-      </c>
-      <c r="F24" s="19">
-        <f>F21+F22</f>
-        <v>14630</v>
-      </c>
-      <c r="G24" s="5">
-        <f>G21+G22</f>
-        <v>3800</v>
-      </c>
-      <c r="I24">
-        <f>F24-4100</f>
-        <v>10530</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>284</v>
-      </c>
-      <c r="B27" t="s">
-        <v>234</v>
-      </c>
-      <c r="C27" s="20">
-        <v>0</v>
-      </c>
-      <c r="D27" s="20">
-        <f>C27+(C27*20%)</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="20">
-        <f>C27*21%</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="20">
-        <f>C27-E27</f>
-        <v>0</v>
-      </c>
-      <c r="G27" s="20">
-        <f>D27-C27</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>285</v>
-      </c>
-      <c r="B28" t="s">
-        <v>361</v>
-      </c>
-      <c r="C28" s="5">
-        <v>8150</v>
-      </c>
-      <c r="D28" s="5">
-        <f>C28+(C28*20%)</f>
-        <v>9780</v>
-      </c>
-      <c r="E28" s="5">
-        <f>C28*21%</f>
-        <v>1711.5</v>
-      </c>
-      <c r="F28" s="5">
-        <f>C28-E28</f>
-        <v>6438.5</v>
-      </c>
-      <c r="G28" s="5">
-        <f>D28-C28</f>
-        <v>1630</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>362</v>
-      </c>
-      <c r="C30">
-        <f>C27+C28</f>
-        <v>8150</v>
-      </c>
-      <c r="D30">
-        <f>D27+D28</f>
-        <v>9780</v>
-      </c>
-      <c r="E30" s="5">
-        <f>E27+E28</f>
-        <v>1711.5</v>
-      </c>
-      <c r="F30" s="19">
-        <f>F27+F28</f>
-        <v>6438.5</v>
-      </c>
-      <c r="G30" s="5">
-        <f>G27+G28</f>
-        <v>1630</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>284</v>
-      </c>
-      <c r="B33" s="24">
-        <v>45658</v>
-      </c>
-      <c r="C33" s="20">
-        <v>0</v>
-      </c>
-      <c r="D33" s="20">
-        <f>C33+(C33*20%)</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="20">
-        <f>C33*21%</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="20">
-        <f>C33-E33</f>
-        <v>0</v>
-      </c>
-      <c r="G33" s="20">
-        <f>D33-C33</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>285</v>
-      </c>
-      <c r="B34" t="s">
-        <v>361</v>
-      </c>
-      <c r="C34" s="5">
-        <f>12800+800</f>
-        <v>13600</v>
-      </c>
-      <c r="D34" s="5">
-        <f>C34+(C34*20%)</f>
-        <v>16320</v>
-      </c>
-      <c r="E34" s="5">
-        <f>C34*26%</f>
-        <v>3536</v>
-      </c>
-      <c r="F34" s="5">
-        <f>C34-E34</f>
-        <v>10064</v>
-      </c>
-      <c r="G34" s="5">
-        <f>D34-C34</f>
-        <v>2720</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>362</v>
-      </c>
-      <c r="C36">
-        <f>C33+C34</f>
-        <v>13600</v>
-      </c>
-      <c r="D36">
-        <f>D33+D34</f>
-        <v>16320</v>
-      </c>
-      <c r="E36" s="5">
-        <f>E33+E34</f>
-        <v>3536</v>
-      </c>
-      <c r="F36" s="19">
-        <f>F33+F34</f>
-        <v>10064</v>
-      </c>
-      <c r="G36" s="5">
-        <f>G33+G34</f>
-        <v>2720</v>
       </c>
     </row>
   </sheetData>
@@ -23775,8 +24554,541 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A0FB8E-CB12-475E-9D50-00930E5BD370}">
+  <dimension ref="A1:J36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.75" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.25" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G1" t="s">
+        <v>283</v>
+      </c>
+      <c r="I1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C2" s="20">
+        <v>9456</v>
+      </c>
+      <c r="D2" s="20">
+        <f>C2+(C2*20%)</f>
+        <v>11347.2</v>
+      </c>
+      <c r="E2" s="20">
+        <f>C2*21%</f>
+        <v>1985.76</v>
+      </c>
+      <c r="F2" s="20">
+        <f>C2-E2</f>
+        <v>7470.24</v>
+      </c>
+      <c r="G2" s="20">
+        <f>D2-C2</f>
+        <v>1891.2000000000007</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <f>C3+(C3*20%)</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <f>C3*21%</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <f>C3-E3</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <f>D3-C3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C5">
+        <f>C2+C3</f>
+        <v>9456</v>
+      </c>
+      <c r="D5">
+        <f>D2+D3</f>
+        <v>11347.2</v>
+      </c>
+      <c r="E5" s="5">
+        <f>E2+E3</f>
+        <v>1985.76</v>
+      </c>
+      <c r="F5" s="19">
+        <f>F2+F3</f>
+        <v>7470.24</v>
+      </c>
+      <c r="G5" s="5">
+        <f>G2+G3</f>
+        <v>1891.2000000000007</v>
+      </c>
+      <c r="I5">
+        <f>E5+G5</f>
+        <v>3876.9600000000009</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>284</v>
+      </c>
+      <c r="B9" t="s">
+        <v>310</v>
+      </c>
+      <c r="C9" s="20">
+        <v>9600</v>
+      </c>
+      <c r="D9" s="20">
+        <f>C9+(C9*20%)</f>
+        <v>11520</v>
+      </c>
+      <c r="E9" s="20">
+        <f>C9*21%</f>
+        <v>2016</v>
+      </c>
+      <c r="F9" s="20">
+        <f>C9-E9</f>
+        <v>7584</v>
+      </c>
+      <c r="G9" s="20">
+        <f>D9-C9</f>
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>285</v>
+      </c>
+      <c r="B10" t="s">
+        <v>310</v>
+      </c>
+      <c r="C10" s="5">
+        <f>1300+3200+600</f>
+        <v>5100</v>
+      </c>
+      <c r="D10" s="5">
+        <f>C10+(C10*20%)</f>
+        <v>6120</v>
+      </c>
+      <c r="E10" s="5">
+        <f>C10*21%</f>
+        <v>1071</v>
+      </c>
+      <c r="F10" s="5">
+        <f>C10-E10</f>
+        <v>4029</v>
+      </c>
+      <c r="G10" s="5">
+        <f>D10-C10</f>
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>312</v>
+      </c>
+      <c r="C12">
+        <f>C9+C10</f>
+        <v>14700</v>
+      </c>
+      <c r="D12">
+        <f>D9+D10</f>
+        <v>17640</v>
+      </c>
+      <c r="E12" s="5">
+        <f>E9+E10</f>
+        <v>3087</v>
+      </c>
+      <c r="F12" s="19">
+        <f>F9+F10</f>
+        <v>11613</v>
+      </c>
+      <c r="G12" s="5">
+        <f>G9+G10</f>
+        <v>2940</v>
+      </c>
+      <c r="I12">
+        <f>E12+G12</f>
+        <v>6027</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>284</v>
+      </c>
+      <c r="B15" t="s">
+        <v>361</v>
+      </c>
+      <c r="C15" s="20">
+        <v>12000</v>
+      </c>
+      <c r="D15" s="20">
+        <f>C15+(C15*20%)</f>
+        <v>14400</v>
+      </c>
+      <c r="E15" s="20">
+        <f>C15*21%</f>
+        <v>2520</v>
+      </c>
+      <c r="F15" s="20">
+        <f>C15-E15</f>
+        <v>9480</v>
+      </c>
+      <c r="G15" s="20">
+        <f>D15-C15</f>
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>285</v>
+      </c>
+      <c r="B16" t="s">
+        <v>361</v>
+      </c>
+      <c r="C16" s="5">
+        <f>3000+3750+3375</f>
+        <v>10125</v>
+      </c>
+      <c r="D16" s="5">
+        <f>C16+(C16*20%)</f>
+        <v>12150</v>
+      </c>
+      <c r="E16" s="5">
+        <f>C16*21%</f>
+        <v>2126.25</v>
+      </c>
+      <c r="F16" s="5">
+        <f>C16-E16</f>
+        <v>7998.75</v>
+      </c>
+      <c r="G16" s="5">
+        <f>D16-C16</f>
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>362</v>
+      </c>
+      <c r="C18">
+        <f>C15+C16</f>
+        <v>22125</v>
+      </c>
+      <c r="D18">
+        <f>D15+D16</f>
+        <v>26550</v>
+      </c>
+      <c r="E18" s="5">
+        <f>E15+E16</f>
+        <v>4646.25</v>
+      </c>
+      <c r="F18" s="19">
+        <f>F15+F16</f>
+        <v>17478.75</v>
+      </c>
+      <c r="G18" s="5">
+        <f>G15+G16</f>
+        <v>4425</v>
+      </c>
+      <c r="I18">
+        <f>F18-4100</f>
+        <v>13378.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>284</v>
+      </c>
+      <c r="B21" t="s">
+        <v>218</v>
+      </c>
+      <c r="C21" s="20">
+        <v>0</v>
+      </c>
+      <c r="D21" s="20">
+        <f>C21+(C21*20%)</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="20">
+        <f>C21*21%</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="20">
+        <f>C21-E21</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="20">
+        <f>D21-C21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>285</v>
+      </c>
+      <c r="B22" t="s">
+        <v>361</v>
+      </c>
+      <c r="C22" s="5">
+        <v>19000</v>
+      </c>
+      <c r="D22" s="5">
+        <f>C22+(C22*20%)</f>
+        <v>22800</v>
+      </c>
+      <c r="E22" s="5">
+        <f>C22*23%</f>
+        <v>4370</v>
+      </c>
+      <c r="F22" s="5">
+        <f>C22-E22</f>
+        <v>14630</v>
+      </c>
+      <c r="G22" s="5">
+        <f>D22-C22</f>
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>362</v>
+      </c>
+      <c r="C24">
+        <f>C21+C22</f>
+        <v>19000</v>
+      </c>
+      <c r="D24">
+        <f>D21+D22</f>
+        <v>22800</v>
+      </c>
+      <c r="E24" s="5">
+        <f>E21+E22</f>
+        <v>4370</v>
+      </c>
+      <c r="F24" s="19">
+        <f>F21+F22</f>
+        <v>14630</v>
+      </c>
+      <c r="G24" s="5">
+        <f>G21+G22</f>
+        <v>3800</v>
+      </c>
+      <c r="I24">
+        <f>F24-4100</f>
+        <v>10530</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>284</v>
+      </c>
+      <c r="B27" t="s">
+        <v>234</v>
+      </c>
+      <c r="C27" s="20">
+        <v>0</v>
+      </c>
+      <c r="D27" s="20">
+        <f>C27+(C27*20%)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="20">
+        <f>C27*21%</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="20">
+        <f>C27-E27</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="20">
+        <f>D27-C27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B28" t="s">
+        <v>361</v>
+      </c>
+      <c r="C28" s="5">
+        <v>8150</v>
+      </c>
+      <c r="D28" s="5">
+        <f>C28+(C28*20%)</f>
+        <v>9780</v>
+      </c>
+      <c r="E28" s="5">
+        <f>C28*21%</f>
+        <v>1711.5</v>
+      </c>
+      <c r="F28" s="5">
+        <f>C28-E28</f>
+        <v>6438.5</v>
+      </c>
+      <c r="G28" s="5">
+        <f>D28-C28</f>
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>362</v>
+      </c>
+      <c r="C30">
+        <f>C27+C28</f>
+        <v>8150</v>
+      </c>
+      <c r="D30">
+        <f>D27+D28</f>
+        <v>9780</v>
+      </c>
+      <c r="E30" s="5">
+        <f>E27+E28</f>
+        <v>1711.5</v>
+      </c>
+      <c r="F30" s="19">
+        <f>F27+F28</f>
+        <v>6438.5</v>
+      </c>
+      <c r="G30" s="5">
+        <f>G27+G28</f>
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>284</v>
+      </c>
+      <c r="B33" s="24">
+        <v>45658</v>
+      </c>
+      <c r="C33" s="20">
+        <v>0</v>
+      </c>
+      <c r="D33" s="20">
+        <f>C33+(C33*20%)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="20">
+        <f>C33*21%</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="20">
+        <f>C33-E33</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="20">
+        <f>D33-C33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>285</v>
+      </c>
+      <c r="B34" t="s">
+        <v>361</v>
+      </c>
+      <c r="C34" s="5">
+        <v>3750</v>
+      </c>
+      <c r="D34" s="5">
+        <f>C34+(C34*20%)</f>
+        <v>4500</v>
+      </c>
+      <c r="E34" s="5">
+        <f>C34*26%</f>
+        <v>975</v>
+      </c>
+      <c r="F34" s="5">
+        <f>C34-E34</f>
+        <v>2775</v>
+      </c>
+      <c r="G34" s="5">
+        <f>D34-C34</f>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>362</v>
+      </c>
+      <c r="C36">
+        <f>C33+C34</f>
+        <v>3750</v>
+      </c>
+      <c r="D36">
+        <f>D33+D34</f>
+        <v>4500</v>
+      </c>
+      <c r="E36" s="5">
+        <f>E33+E34</f>
+        <v>975</v>
+      </c>
+      <c r="F36" s="19">
+        <f>F33+F34</f>
+        <v>2775</v>
+      </c>
+      <c r="G36" s="5">
+        <f>G33+G34</f>
+        <v>750</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94700D3-58F8-480F-AA59-9339E917FDF7}">
-  <dimension ref="A1:O88"/>
+  <dimension ref="A1:R93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
@@ -23785,6 +25097,7 @@
     <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.75" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -24487,7 +25800,7 @@
         <v>1310000</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>411</v>
       </c>
@@ -24498,7 +25811,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>407</v>
       </c>
@@ -24511,7 +25824,7 @@
         <v>429500</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>408</v>
       </c>
@@ -24522,7 +25835,7 @@
         <v>396250</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>409</v>
       </c>
@@ -24533,7 +25846,7 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>410</v>
       </c>
@@ -24544,7 +25857,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>412</v>
       </c>
@@ -24554,8 +25867,20 @@
       <c r="C71" s="5">
         <v>260000</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="H71" t="s">
+        <v>453</v>
+      </c>
+      <c r="K71" t="s">
+        <v>445</v>
+      </c>
+      <c r="N71" t="s">
+        <v>446</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>416</v>
       </c>
@@ -24565,8 +25890,36 @@
       <c r="C72" s="5">
         <v>200000</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="H72" t="s">
+        <v>270</v>
+      </c>
+      <c r="I72">
+        <f>1.4*3.9</f>
+        <v>5.46</v>
+      </c>
+      <c r="K72" t="s">
+        <v>437</v>
+      </c>
+      <c r="L72">
+        <f>3.4*3.9</f>
+        <v>13.26</v>
+      </c>
+      <c r="N72" t="s">
+        <v>447</v>
+      </c>
+      <c r="O72">
+        <f>1.66*1.66</f>
+        <v>2.7555999999999998</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>450</v>
+      </c>
+      <c r="R72">
+        <f>(1.6*3)*4</f>
+        <v>19.200000000000003</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>414</v>
       </c>
@@ -24578,8 +25931,29 @@
         <f>250000+60000</f>
         <v>310000</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K73" t="s">
+        <v>438</v>
+      </c>
+      <c r="L73">
+        <f>3.4*3.9</f>
+        <v>13.26</v>
+      </c>
+      <c r="N73" t="s">
+        <v>448</v>
+      </c>
+      <c r="O73">
+        <f>1.66*1.8</f>
+        <v>2.988</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>451</v>
+      </c>
+      <c r="R73">
+        <f>(1.6*3)*2+(1.8*3)*2</f>
+        <v>20.400000000000002</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>422</v>
       </c>
@@ -24587,11 +25961,25 @@
         <v>2100000</v>
       </c>
       <c r="C74">
-        <f>500000+200000+300000+200000</f>
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+        <f>500000+200000+300000+200000+100000</f>
+        <v>1300000</v>
+      </c>
+      <c r="K74" t="s">
+        <v>439</v>
+      </c>
+      <c r="L74">
+        <f>5.56*3.9</f>
+        <v>21.683999999999997</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>452</v>
+      </c>
+      <c r="R74">
+        <f>(1.4*3)+(3.9*3)*2</f>
+        <v>27.599999999999998</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>423</v>
       </c>
@@ -24600,11 +25988,21 @@
         <v>795000</v>
       </c>
       <c r="C75">
-        <f>73000+73000+73000+73000+73000</f>
-        <v>365000</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+        <f>73000+73000+73000+73000+73000+88000</f>
+        <v>453000</v>
+      </c>
+      <c r="K75" t="s">
+        <v>440</v>
+      </c>
+      <c r="L75">
+        <f>1.4*16</f>
+        <v>22.4</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>432</v>
       </c>
@@ -24612,85 +26010,195 @@
         <v>675000</v>
       </c>
       <c r="C76">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+        <f>300000+150000</f>
+        <v>450000</v>
+      </c>
+      <c r="K76" t="s">
+        <v>441</v>
+      </c>
+      <c r="L76">
+        <f>3*5</f>
+        <v>15</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>431</v>
       </c>
       <c r="C77">
-        <f>201000+150000</f>
-        <v>351000</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+        <f>300000+201000+150000</f>
+        <v>651000</v>
+      </c>
+      <c r="K77" t="s">
+        <v>442</v>
+      </c>
+      <c r="L77">
+        <f>1*3.9</f>
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>434</v>
       </c>
       <c r="B78">
         <v>1000000</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K78" t="s">
+        <v>443</v>
+      </c>
+      <c r="L78">
+        <f>2*2</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>435</v>
       </c>
       <c r="B79">
         <v>400000</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K79" t="s">
+        <v>444</v>
+      </c>
+      <c r="L79">
+        <f>3*2</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>436</v>
+      </c>
+      <c r="C80">
+        <f>155000</f>
+        <v>155000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>433</v>
       </c>
-      <c r="C80">
+      <c r="C81">
         <f>200000</f>
         <v>200000</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>6</v>
       </c>
-      <c r="B82">
-        <f>SUM(B67:B80)</f>
+      <c r="B83">
+        <f>SUM(B67:B81)</f>
         <v>7595750</v>
       </c>
-      <c r="C82">
-        <f>SUM(C67:C80)</f>
-        <v>4761750</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="C83">
+        <f>SUM(C67:C81)</f>
+        <v>5554750</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>421</v>
       </c>
-      <c r="B83">
-        <f>B82/655</f>
+      <c r="B84">
+        <f>B83/655</f>
         <v>11596.564885496184</v>
       </c>
-      <c r="C83">
-        <f>C82/655</f>
-        <v>7269.8473282442746</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="C84">
+        <f>C83/655</f>
+        <v>8480.5343511450374</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H85" t="s">
+        <v>454</v>
+      </c>
+      <c r="I85">
+        <f>I72</f>
+        <v>5.46</v>
+      </c>
+      <c r="K85" t="s">
+        <v>6</v>
+      </c>
+      <c r="L85">
+        <f>SUM(L72:L84)</f>
+        <v>99.503999999999991</v>
+      </c>
+      <c r="N85" t="s">
+        <v>6</v>
+      </c>
+      <c r="O85">
+        <f t="shared" ref="O85" si="0">SUM(O72:O84)</f>
+        <v>5.7435999999999998</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>175</v>
+      </c>
+      <c r="R85">
+        <f t="shared" ref="R85" si="1">SUM(R72:R84)</f>
+        <v>67.2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I86">
+        <v>6</v>
+      </c>
+      <c r="L86">
+        <v>100</v>
+      </c>
+      <c r="O86">
+        <v>6</v>
+      </c>
+      <c r="R86">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>417</v>
       </c>
-      <c r="B86">
+      <c r="B87">
         <f>2000+4000+3000</f>
         <v>9000</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>99</v>
       </c>
-      <c r="B88">
-        <f>B86-C83</f>
-        <v>1730.1526717557254</v>
+      <c r="B89">
+        <f>B87-C84</f>
+        <v>519.46564885496264</v>
+      </c>
+      <c r="I89">
+        <f>I86*3500</f>
+        <v>21000</v>
+      </c>
+      <c r="L89">
+        <f>L86*7000</f>
+        <v>700000</v>
+      </c>
+      <c r="O89">
+        <f>O86*3500</f>
+        <v>21000</v>
+      </c>
+      <c r="R89">
+        <f>R86*3500</f>
+        <v>234500</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="K93" t="s">
+        <v>175</v>
+      </c>
+      <c r="M93">
+        <f>I89+L89+O89+R89</f>
+        <v>976500</v>
       </c>
     </row>
   </sheetData>
@@ -24698,7 +26206,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949D250C-39B2-4E80-98CE-CD0726DE900E}">
   <dimension ref="A3:G22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -24928,7 +26436,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A9C44F7-AFBE-4C6B-AF7F-6A7B39EB63FD}">
   <dimension ref="A2:P29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -25162,7 +26670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31B0527-2C58-45D2-85E0-B2079F911CE6}">
   <dimension ref="A2:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -25263,7 +26771,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60023A54-4F93-427E-93E6-1AE8B5C3C1AA}">
   <dimension ref="B3:H19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -25389,7 +26897,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3206B880-2680-4A84-A754-F93B2E76569E}">
   <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>

--- a/Budget1.xlsx
+++ b/Budget1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\NewGit\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F77F377-436D-4DA8-9702-E800F68C8504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0816D57-3D7F-4C90-BB88-530C800323FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="27" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1727" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="456">
   <si>
     <t>Loyer</t>
   </si>
@@ -1434,6 +1434,9 @@
   </si>
   <si>
     <t xml:space="preserve">total </t>
+  </si>
+  <si>
+    <t>escalier</t>
   </si>
 </sst>
 </file>
@@ -22632,8 +22635,8 @@
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11">
-        <f>2200+3000+1000</f>
-        <v>6200</v>
+        <f>2200+3000+900</f>
+        <v>6100</v>
       </c>
       <c r="I4" s="11"/>
       <c r="J4" s="12"/>
@@ -23426,7 +23429,7 @@
       </c>
       <c r="C34" s="11">
         <f>H4-D26</f>
-        <v>953</v>
+        <v>853</v>
       </c>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
@@ -25890,13 +25893,6 @@
       <c r="C72" s="5">
         <v>200000</v>
       </c>
-      <c r="H72" t="s">
-        <v>270</v>
-      </c>
-      <c r="I72">
-        <f>1.4*3.9</f>
-        <v>5.46</v>
-      </c>
       <c r="K72" t="s">
         <v>437</v>
       </c>
@@ -25961,8 +25957,8 @@
         <v>2100000</v>
       </c>
       <c r="C74">
-        <f>500000+200000+300000+200000+100000</f>
-        <v>1300000</v>
+        <f>500000+200000+300000+200000+100000+250000</f>
+        <v>1550000</v>
       </c>
       <c r="K74" t="s">
         <v>439</v>
@@ -26078,6 +26074,13 @@
         <f>155000</f>
         <v>155000</v>
       </c>
+      <c r="K80" t="s">
+        <v>270</v>
+      </c>
+      <c r="L80">
+        <f>1.4*3.9</f>
+        <v>5.46</v>
+      </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
@@ -26087,6 +26090,13 @@
         <f>200000</f>
         <v>200000</v>
       </c>
+      <c r="K81" t="s">
+        <v>455</v>
+      </c>
+      <c r="L81">
+        <f>(0.5*1)*20</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
@@ -26098,7 +26108,7 @@
       </c>
       <c r="C83">
         <f>SUM(C67:C81)</f>
-        <v>5554750</v>
+        <v>5804750</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
@@ -26111,23 +26121,19 @@
       </c>
       <c r="C84">
         <f>C83/655</f>
-        <v>8480.5343511450374</v>
+        <v>8862.2137404580153</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="H85" t="s">
         <v>454</v>
       </c>
-      <c r="I85">
-        <f>I72</f>
-        <v>5.46</v>
-      </c>
       <c r="K85" t="s">
         <v>6</v>
       </c>
       <c r="L85">
         <f>SUM(L72:L84)</f>
-        <v>99.503999999999991</v>
+        <v>114.96399999999998</v>
       </c>
       <c r="N85" t="s">
         <v>6</v>
@@ -26149,7 +26155,7 @@
         <v>6</v>
       </c>
       <c r="L86">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="O86">
         <v>6</v>
@@ -26163,8 +26169,8 @@
         <v>417</v>
       </c>
       <c r="B87">
-        <f>2000+4000+3000</f>
-        <v>9000</v>
+        <f>2000+4000+3000+800</f>
+        <v>9800</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
@@ -26173,23 +26179,19 @@
       </c>
       <c r="B89">
         <f>B87-C84</f>
-        <v>519.46564885496264</v>
-      </c>
-      <c r="I89">
-        <f>I86*3500</f>
-        <v>21000</v>
+        <v>937.78625954198469</v>
       </c>
       <c r="L89">
         <f>L86*7000</f>
-        <v>700000</v>
+        <v>910000</v>
       </c>
       <c r="O89">
-        <f>O86*3500</f>
-        <v>21000</v>
+        <f>O86*5000</f>
+        <v>30000</v>
       </c>
       <c r="R89">
-        <f>R86*3500</f>
-        <v>234500</v>
+        <f>R86*5500</f>
+        <v>368500</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
@@ -26198,7 +26200,7 @@
       </c>
       <c r="M93">
         <f>I89+L89+O89+R89</f>
-        <v>976500</v>
+        <v>1308500</v>
       </c>
     </row>
   </sheetData>

--- a/Budget1.xlsx
+++ b/Budget1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\NewGit\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0816D57-3D7F-4C90-BB88-530C800323FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B71E49E-E63F-4440-AF86-988B5FA88097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="27" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="30" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
   <sheets>
     <sheet name="Fevrier" sheetId="3" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1729" uniqueCount="457">
   <si>
     <t>Loyer</t>
   </si>
@@ -1437,6 +1437,9 @@
   </si>
   <si>
     <t>escalier</t>
+  </si>
+  <si>
+    <t>Terrassement</t>
   </si>
 </sst>
 </file>
@@ -25091,7 +25094,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94700D3-58F8-480F-AA59-9339E917FDF7}">
-  <dimension ref="A1:R93"/>
+  <dimension ref="A1:R94"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
@@ -26084,122 +26087,131 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>456</v>
+      </c>
+      <c r="C81">
+        <f>292000</f>
+        <v>292000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>433</v>
       </c>
-      <c r="C81">
+      <c r="C82">
         <f>200000</f>
         <v>200000</v>
       </c>
-      <c r="K81" t="s">
+      <c r="K82" t="s">
         <v>455</v>
       </c>
-      <c r="L81">
+      <c r="L82">
         <f>(0.5*1)*20</f>
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>6</v>
-      </c>
-      <c r="B83">
-        <f>SUM(B67:B81)</f>
-        <v>7595750</v>
-      </c>
-      <c r="C83">
-        <f>SUM(C67:C81)</f>
-        <v>5804750</v>
-      </c>
-    </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84">
+        <f>SUM(B67:B82)</f>
+        <v>7595750</v>
+      </c>
+      <c r="C84">
+        <f>SUM(C67:C82)</f>
+        <v>6096750</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>421</v>
       </c>
-      <c r="B84">
-        <f>B83/655</f>
+      <c r="B85">
+        <f>B84/655</f>
         <v>11596.564885496184</v>
       </c>
-      <c r="C84">
-        <f>C83/655</f>
-        <v>8862.2137404580153</v>
-      </c>
-    </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="H85" t="s">
+      <c r="C85">
+        <f>C84/655</f>
+        <v>9308.0152671755732</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H86" t="s">
         <v>454</v>
       </c>
-      <c r="K85" t="s">
+      <c r="K86" t="s">
         <v>6</v>
       </c>
-      <c r="L85">
-        <f>SUM(L72:L84)</f>
+      <c r="L86">
+        <f>SUM(L72:L85)</f>
         <v>114.96399999999998</v>
       </c>
-      <c r="N85" t="s">
+      <c r="N86" t="s">
         <v>6</v>
       </c>
-      <c r="O85">
-        <f t="shared" ref="O85" si="0">SUM(O72:O84)</f>
+      <c r="O86">
+        <f t="shared" ref="O86" si="0">SUM(O72:O85)</f>
         <v>5.7435999999999998</v>
       </c>
-      <c r="Q85" t="s">
+      <c r="Q86" t="s">
         <v>175</v>
       </c>
-      <c r="R85">
-        <f t="shared" ref="R85" si="1">SUM(R72:R84)</f>
+      <c r="R86">
+        <f t="shared" ref="R86" si="1">SUM(R72:R85)</f>
         <v>67.2</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="I86">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I87">
         <v>6</v>
       </c>
-      <c r="L86">
+      <c r="L87">
         <v>130</v>
       </c>
-      <c r="O86">
+      <c r="O87">
         <v>6</v>
       </c>
-      <c r="R86">
+      <c r="R87">
         <v>67</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>417</v>
       </c>
-      <c r="B87">
+      <c r="B88">
         <f>2000+4000+3000+800</f>
         <v>9800</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>99</v>
       </c>
-      <c r="B89">
-        <f>B87-C84</f>
-        <v>937.78625954198469</v>
-      </c>
-      <c r="L89">
-        <f>L86*7000</f>
+      <c r="B90">
+        <f>B88-C85</f>
+        <v>491.98473282442683</v>
+      </c>
+      <c r="L90">
+        <f>L87*7000</f>
         <v>910000</v>
       </c>
-      <c r="O89">
-        <f>O86*5000</f>
+      <c r="O90">
+        <f>O87*5000</f>
         <v>30000</v>
       </c>
-      <c r="R89">
-        <f>R86*5500</f>
+      <c r="R90">
+        <f>R87*5500</f>
         <v>368500</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K93" t="s">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="K94" t="s">
         <v>175</v>
       </c>
-      <c r="M93">
-        <f>I89+L89+O89+R89</f>
+      <c r="M94">
+        <f>I90+L90+O90+R90</f>
         <v>1308500</v>
       </c>
     </row>

--- a/Budget1.xlsx
+++ b/Budget1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\NewGit\myDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B71E49E-E63F-4440-AF86-988B5FA88097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5918A642-55CA-4144-8C0D-BB1BBE208403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="30" xr2:uid="{27B7E826-E620-B34C-81E1-46A3DBC74E62}"/>
   </bookViews>
@@ -25960,8 +25960,8 @@
         <v>2100000</v>
       </c>
       <c r="C74">
-        <f>500000+200000+300000+200000+100000+250000</f>
-        <v>1550000</v>
+        <f>500000+200000+300000+200000+100000+250000+150000</f>
+        <v>1700000</v>
       </c>
       <c r="K74" t="s">
         <v>439</v>
@@ -26120,7 +26120,7 @@
       </c>
       <c r="C84">
         <f>SUM(C67:C82)</f>
-        <v>6096750</v>
+        <v>6246750</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
@@ -26133,7 +26133,7 @@
       </c>
       <c r="C85">
         <f>C84/655</f>
-        <v>9308.0152671755732</v>
+        <v>9537.0229007633588</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
@@ -26191,7 +26191,7 @@
       </c>
       <c r="B90">
         <f>B88-C85</f>
-        <v>491.98473282442683</v>
+        <v>262.97709923664115</v>
       </c>
       <c r="L90">
         <f>L87*7000</f>
